--- a/setup/product-import/product-import-workbook.xlsx
+++ b/setup/product-import/product-import-workbook.xlsx
@@ -209,12 +209,12 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>The product's barcode (EAN, usually 13 digits). The whole store keeps the barcode here. This column is formatted as text so Excel keeps every digit.</t>
+        <t>The product's barcode (EAN, usually 13 digits). The store shows it under the title. Formatted as text so Excel keeps every digit.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Leave blank. The barcode goes in SKU.</t>
+        <t>The same barcode again, exactly as in SKU. Google reads this one.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -612,7 +612,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BARCODE goes in the SKU column, not the Barcodes column. That is how every product already on the store is set up. The SKU column is formatted as text so Excel does not turn 5012345678900 into 5.01E+12 or drop a leading zero.</t>
+          <t>BARCODE goes in BOTH the SKU column and the Barcodes column, the same number in each. SKU is what the product page shows; Barcodes is what Google reads. Both columns are formatted as text so Excel does not turn 5012345678900 into 5.01E+12 or drop a leading zero. A bundle made up in the shop has no barcode of its own: leave Barcodes blank rather than inventing one. (A boxed gift set from the brand has a real barcode on the box; use that.)</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,11 @@
           <t>5012345678900</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>5012345678900</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
           <t>12.99</t>
@@ -4785,7 +4789,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>505</v>
+        <v>332</v>
       </c>
     </row>
     <row r="117">
